--- a/public/insumos_template.xlsx
+++ b/public/insumos_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t xml:space="preserve">marca_comercial</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t xml:space="preserve">unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio</t>
   </si>
   <si>
     <t xml:space="preserve">DUOZOLE ZURCOS</t>
@@ -144,29 +147,28 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="8.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -185,39 +187,48 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
